--- a/Result/profitability/8473.xlsx
+++ b/Result/profitability/8473.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM48"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6526,6 +6526,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1081</v>
+      </c>
+      <c r="D49" t="n">
+        <v>728</v>
+      </c>
+      <c r="E49" t="n">
+        <v>352</v>
+      </c>
+      <c r="F49" t="n">
+        <v>32.61</v>
+      </c>
+      <c r="G49" t="n">
+        <v>282</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>26.10%</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J49" t="n">
+        <v>259</v>
+      </c>
+      <c r="K49" t="n">
+        <v>218</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="N49" t="n">
+        <v>23.84375</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="X49" t="n">
+        <v>-0.02439024390243905</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>-0.259999999999998</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>-0.00790994828110736</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.033898305084746</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.390000000000001</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.1160164271047228</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
